--- a/templates/INFRA Y MAST - template.xlsx
+++ b/templates/INFRA Y MAST - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$42</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1249,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="54" min="1" max="1"/>
@@ -1257,8 +1257,8 @@
     <col width="5.42578125" customWidth="1" style="54" min="7" max="7"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="54" min="8" max="8"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="54" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="54" min="10" max="17"/>
-    <col width="9.140625" customWidth="1" style="54" min="18" max="16384"/>
+    <col width="9.140625" customWidth="1" style="54" min="10" max="18"/>
+    <col width="9.140625" customWidth="1" style="54" min="19" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -1402,20 +1402,20 @@
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="38" t="n">
-        <v>1.194638538582</v>
+        <v>1.203314483628</v>
       </c>
       <c r="D17" s="37" t="n">
-        <v>7.336653809275617e-05</v>
+        <v>0.002486689073489146</v>
       </c>
       <c r="E17" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>0.1351973962440817</v>
+        <v>4.582387240069794</v>
       </c>
       <c r="G17" s="4" t="n"/>
     </row>
@@ -1423,20 +1423,20 @@
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1.194550898518</v>
+        <v>1.200329637035</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.0004714877114151417</v>
+        <v>0.0006340317883168911</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.8688417444996206</v>
+        <v>1.16837251892748</v>
       </c>
       <c r="G18" s="4" t="n"/>
     </row>
@@ -1444,20 +1444,20 @@
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1.193987947873</v>
+        <v>1.199569072111</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.0005659693329573834</v>
+        <v>0.001527562209878042</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>1.042949308485811</v>
+        <v>2.814940417595601</v>
       </c>
       <c r="G19" s="4" t="n"/>
     </row>
@@ -1465,20 +1465,20 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1.193312569554</v>
+        <v>1.197739450589</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.0005472435186237856</v>
+        <v>-0.000375114655707165</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>1.008442005752626</v>
+        <v>-0.6912487090570673</v>
       </c>
       <c r="G20" s="4" t="n"/>
     </row>
@@ -1486,20 +1486,20 @@
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1.192659894157</v>
+        <v>1.198188908809</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.001205592113070475</v>
+        <v>0.0007643154843783861</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>2.221624719616173</v>
+        <v>1.408454945309659</v>
       </c>
       <c r="G21" s="4" t="n"/>
     </row>
@@ -1540,18 +1540,18 @@
     <row r="24" ht="15.95" customHeight="1">
       <c r="B24" s="39" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="39" t="inlineStr"/>
       <c r="D24" s="37" t="n">
-        <v>0.006897585929224181</v>
+        <v>0.005715907999036762</v>
       </c>
       <c r="E24" s="37" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.6579551801266765</v>
+        <v>1.502278324657221</v>
       </c>
       <c r="G24" s="17" t="n"/>
     </row>
@@ -1564,13 +1564,13 @@
       </c>
       <c r="C25" s="40" t="inlineStr"/>
       <c r="D25" s="12" t="n">
-        <v>0.008512881375644543</v>
+        <v>0.01034641292271976</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.7340048077572356</v>
+        <v>0.8988735572214778</v>
       </c>
       <c r="G25" s="19" t="n"/>
     </row>
@@ -1583,13 +1583,13 @@
       </c>
       <c r="C26" s="40" t="inlineStr"/>
       <c r="D26" s="12" t="n">
-        <v>0.03441025156514943</v>
+        <v>0.03804380022287068</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.9751223426775759</v>
+        <v>1.080831048861978</v>
       </c>
       <c r="G26" s="19" t="n"/>
     </row>
@@ -1602,13 +1602,13 @@
       </c>
       <c r="C27" s="40" t="inlineStr"/>
       <c r="D27" s="46" t="n">
-        <v>0.07878366550673443</v>
+        <v>0.07469587397852129</v>
       </c>
       <c r="E27" s="46" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>1.096229600388562</v>
+        <v>1.040691857552856</v>
       </c>
       <c r="G27" s="19" t="n"/>
     </row>
@@ -1621,13 +1621,13 @@
       </c>
       <c r="C28" s="40" t="inlineStr"/>
       <c r="D28" s="46" t="n">
-        <v>0.1830371002545321</v>
+        <v>0.1838192923927788</v>
       </c>
       <c r="E28" s="46" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>1.238268735133284</v>
+        <v>1.241887683484013</v>
       </c>
       <c r="G28" s="4" t="n"/>
     </row>
@@ -1640,13 +1640,13 @@
       </c>
       <c r="C29" s="40" t="inlineStr"/>
       <c r="D29" s="46" t="n">
-        <v>0.03163495698089713</v>
+        <v>0.03912710452614787</v>
       </c>
       <c r="E29" s="46" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>0.9752129443230492</v>
+        <v>1.028162118797032</v>
       </c>
       <c r="G29" s="4" t="n"/>
     </row>
@@ -1678,153 +1678,147 @@
       </c>
       <c r="C31" s="40" t="inlineStr"/>
       <c r="D31" s="46" t="n">
-        <v>0.194638538582</v>
+        <v>0.2033144836280001</v>
       </c>
       <c r="E31" s="46" t="n">
-        <v>0.1553170478267938</v>
+        <v>0.1616018506845176</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>1.253169187190943</v>
+        <v>1.258119772557028</v>
       </c>
       <c r="G31" s="4" t="n"/>
     </row>
-    <row r="32"/>
-    <row r="33" ht="26.1" customHeight="1">
-      <c r="A33" s="20" t="n"/>
-      <c r="B33" s="53" t="inlineStr">
+    <row r="32" ht="15.95" customHeight="1"/>
+    <row r="33"/>
+    <row r="34" ht="26.1" customHeight="1">
+      <c r="A34" s="20" t="n"/>
+      <c r="B34" s="53" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="15.95" customHeight="1">
-      <c r="A34" s="23" t="n"/>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="41" t="n">
-        <v>189571618.4547</v>
-      </c>
-      <c r="F34" s="41" t="n"/>
       <c r="G34" s="4" t="n"/>
     </row>
     <row r="35" ht="15.95" customHeight="1">
       <c r="A35" s="23" t="n"/>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="41" t="n">
-        <v>185413714.7599186</v>
-      </c>
-      <c r="F35" s="41" t="n"/>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>190771544.5053</v>
+      </c>
       <c r="G35" s="4" t="n"/>
     </row>
     <row r="36" ht="15.95" customHeight="1">
       <c r="A36" s="23" t="n"/>
-      <c r="B36" s="25" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="41" t="n">
+        <v>188589040.7374774</v>
+      </c>
+      <c r="F36" s="41" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
-      <c r="A37" s="29" t="n"/>
-      <c r="B37" s="26" t="inlineStr">
+      <c r="A37" s="23" t="n"/>
+      <c r="B37" s="25" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="15.95" customHeight="1">
+      <c r="A38" s="29" t="n"/>
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>¹Data de Referência:</t>
         </is>
       </c>
-      <c r="C37" s="27" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D37" s="28" t="n"/>
-      <c r="E37" s="28" t="n"/>
-      <c r="F37" s="28" t="n"/>
-      <c r="G37" s="4" t="n"/>
-    </row>
-    <row r="38" ht="15.95" customHeight="1">
-      <c r="B38" s="27" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="15.95" customHeight="1">
+      <c r="B39" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C38" s="27" t="inlineStr">
+      <c r="C39" s="27" t="inlineStr">
         <is>
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="D38" s="30" t="n"/>
-      <c r="E38" s="30" t="n"/>
-      <c r="F38" s="30" t="n"/>
-      <c r="G38" s="4" t="n"/>
-    </row>
-    <row r="39" ht="15.95" customHeight="1">
-      <c r="B39" s="31" t="n"/>
-      <c r="C39" s="32" t="n"/>
       <c r="D39" s="30" t="n"/>
       <c r="E39" s="30" t="n"/>
       <c r="F39" s="30" t="n"/>
       <c r="G39" s="4" t="n"/>
     </row>
-    <row r="40" ht="54" customHeight="1">
-      <c r="A40" s="4" t="n"/>
-      <c r="B40" s="56" t="inlineStr">
+    <row r="40" ht="15.95" customHeight="1">
+      <c r="B40" s="31" t="n"/>
+      <c r="C40" s="32" t="n"/>
+      <c r="D40" s="30" t="n"/>
+      <c r="E40" s="30" t="n"/>
+      <c r="F40" s="30" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41" ht="54" customHeight="1">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="56" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="55" t="n"/>
       <c r="G41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n"/>
-      <c r="B42" s="33" t="n"/>
-      <c r="C42" s="33" t="n"/>
-      <c r="D42" s="33" t="n"/>
-      <c r="E42" s="33" t="n"/>
-      <c r="F42" s="33" t="n"/>
+      <c r="B42" s="55" t="n"/>
       <c r="G42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="34" t="n"/>
-      <c r="C43" s="35" t="n"/>
-      <c r="D43" s="19" t="n"/>
-      <c r="E43" s="19" t="n"/>
-      <c r="F43" s="19" t="n"/>
+      <c r="B43" s="33" t="n"/>
       <c r="G43" s="4" t="n"/>
     </row>
     <row r="44">
+      <c r="A44" s="4" t="n"/>
       <c r="B44" s="34" t="n"/>
       <c r="C44" s="35" t="n"/>
       <c r="D44" s="19" t="n"/>
       <c r="E44" s="19" t="n"/>
       <c r="F44" s="19" t="n"/>
+      <c r="G44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="34" t="n"/>
+      <c r="C45" s="35" t="n"/>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B34:F34"/>
     <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B42:F42"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="88"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="86"/>
 </worksheet>
 </file>